--- a/analysis/analysis.xlsx
+++ b/analysis/analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasaray/Desktop/TeX/Physics_Laboratory/douji_sokutei/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasaray/Desktop/TeX/Physics_Laboratory/douji_sokutei/analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D8761B-CB27-F842-BF84-3F66C27A07DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17F684A-737F-F94E-86F5-1684C16BD2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="3" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
+    <workbookView xWindow="800" yWindow="680" windowWidth="28600" windowHeight="18440" activeTab="2" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -403,7 +403,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -418,18 +418,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4837,7 +4825,7 @@
         <v>122</v>
       </c>
       <c r="C23">
-        <f t="shared" ref="C22:C26" si="2">B23/(1+$F$10/(2*B23))</f>
+        <f t="shared" ref="C23:C26" si="2">B23/(1+$F$10/(2*B23))</f>
         <v>39.427814569536423</v>
       </c>
       <c r="F23">
@@ -4845,7 +4833,7 @@
         <v>3.7878664857879132</v>
       </c>
       <c r="G23">
-        <f t="shared" ref="G22:G26" si="3">B23/(1+(2*B23)/$F$10)</f>
+        <f t="shared" ref="G23:G26" si="3">B23/(1+(2*B23)/$F$10)</f>
         <v>82.572185430463577</v>
       </c>
       <c r="J23">
@@ -5277,15 +5265,15 @@
         <v>21.5</v>
       </c>
       <c r="G6">
-        <f t="shared" ref="G6:G10" si="0">$J$5*F6</f>
+        <f>$J$5*F6</f>
         <v>82.750867549058711</v>
       </c>
       <c r="H6">
-        <f t="shared" ref="H6:H10" si="1">G6/E6</f>
+        <f t="shared" ref="H6:H10" si="0">G6/E6</f>
         <v>6.4765752437467669E-2</v>
       </c>
       <c r="I6">
-        <f t="shared" ref="I6:I10" si="2">1/SQRT(E6)</f>
+        <f t="shared" ref="I6:I10" si="1">1/SQRT(E6)</f>
         <v>2.7976052219496606E-2</v>
       </c>
       <c r="J6">
@@ -5313,7 +5301,7 @@
         <v>4.5</v>
       </c>
       <c r="G7">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G6:G10" si="2">$J$5*F7</f>
         <v>17.319949021896008</v>
       </c>
       <c r="H7">
@@ -5321,7 +5309,7 @@
         <v>0.14532268678822086</v>
       </c>
       <c r="I7">
-        <f t="shared" si="2"/>
+        <f>1/SQRT(E7)</f>
         <v>9.1599563607362294E-2</v>
       </c>
     </row>
@@ -5336,22 +5324,22 @@
         <v>308</v>
       </c>
       <c r="E8">
-        <f t="shared" ref="E6:E10" si="3">D8*$J$5+$K$5</f>
+        <f t="shared" ref="E8:E10" si="3">D8*$J$5+$K$5</f>
         <v>1169.9262660074314</v>
       </c>
       <c r="F8">
         <v>16.5</v>
       </c>
       <c r="G8">
+        <f t="shared" si="2"/>
+        <v>63.506479746952031</v>
+      </c>
+      <c r="H8">
         <f t="shared" si="0"/>
-        <v>63.506479746952031</v>
-      </c>
-      <c r="H8">
+        <v>5.4282463427099976E-2</v>
+      </c>
+      <c r="I8">
         <f t="shared" si="1"/>
-        <v>5.4282463427099976E-2</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="2"/>
         <v>2.9236188564454289E-2</v>
       </c>
     </row>
@@ -5370,15 +5358,15 @@
         <v>20</v>
       </c>
       <c r="G9">
+        <f t="shared" si="2"/>
+        <v>76.977551208426704</v>
+      </c>
+      <c r="H9">
         <f t="shared" si="0"/>
-        <v>76.977551208426704</v>
-      </c>
-      <c r="H9">
+        <v>5.7809220531698971E-2</v>
+      </c>
+      <c r="I9">
         <f t="shared" si="1"/>
-        <v>5.7809220531698971E-2</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="2"/>
         <v>2.7404161051413384E-2</v>
       </c>
     </row>
@@ -5400,15 +5388,15 @@
         <v>16</v>
       </c>
       <c r="G10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>61.582040966741367</v>
       </c>
       <c r="H10">
+        <f>G10/E10</f>
+        <v>9.1972221242502067E-2</v>
+      </c>
+      <c r="I10">
         <f t="shared" si="1"/>
-        <v>9.1972221242502067E-2</v>
-      </c>
-      <c r="I10">
-        <f t="shared" si="2"/>
         <v>3.8645710707761918E-2</v>
       </c>
     </row>
@@ -5447,10 +5435,10 @@
       <c r="C4" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4">
         <v>1.9230217530069063</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4">
         <v>9.4693284754248452</v>
       </c>
     </row>
@@ -5578,48 +5566,48 @@
     </row>
     <row r="2" spans="1:9" ht="21" thickBot="1"/>
     <row r="3" spans="1:9">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="8"/>
+      <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="5" t="s">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>0.99998565567891595</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="5" t="s">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>0.99997131156359154</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="5" t="s">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>0.99996772550904045</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="5" t="s">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>0.8600138087010355</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="21" thickBot="1">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="1">
         <v>10</v>
       </c>
     </row>
@@ -5629,156 +5617,154 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7" t="s">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="5" t="s">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12">
         <v>206244.08300999075</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12">
         <v>206244.08300999075</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12">
         <v>278850.0000000156</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12">
         <v>1.8522114878870002E-19</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="5" t="s">
+      <c r="A13" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13">
         <v>5.9169900092516903</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13">
         <v>0.73962375115646128</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:9" ht="21" thickBot="1">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="1">
         <v>9</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="1">
         <v>206250</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
     </row>
     <row r="15" spans="1:9" ht="21" thickBot="1"/>
     <row r="16" spans="1:9">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7" t="s">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="5" t="s">
+      <c r="A17" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17">
         <v>9.4693284754248452</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17">
         <v>0.58169221916100677</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17">
         <v>16.278932678664258</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17">
         <v>2.0403247101735171E-7</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17">
         <v>8.1279438126234744</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17">
         <v>10.810713138226216</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17">
         <v>8.1279438126234744</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17">
         <v>10.810713138226216</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="21" thickBot="1">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="1">
         <v>1.9230217530069063</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="1">
         <v>3.6416556117431337E-3</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="1">
         <v>528.06249630135198</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="1">
         <v>1.8522114878870134E-19</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="1">
         <v>1.9146240801072372</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="1">
         <v>1.9314194259065753</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="1">
         <v>1.9146240801072372</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="1">
         <v>1.9314194259065753</v>
       </c>
     </row>

--- a/analysis/analysis.xlsx
+++ b/analysis/analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasaray/Desktop/TeX/Physics_Laboratory/douji_sokutei/analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17F684A-737F-F94E-86F5-1684C16BD2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97511708-4ABD-9947-AB0F-D84F586F3845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="800" yWindow="680" windowWidth="28600" windowHeight="18440" activeTab="2" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
+    <workbookView xWindow="800" yWindow="680" windowWidth="28600" windowHeight="18440" activeTab="4" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5269,7 +5269,7 @@
         <v>82.750867549058711</v>
       </c>
       <c r="H6">
-        <f t="shared" ref="H6:H10" si="0">G6/E6</f>
+        <f t="shared" ref="H6:H9" si="0">G6/E6</f>
         <v>6.4765752437467669E-2</v>
       </c>
       <c r="I6">
@@ -5301,7 +5301,7 @@
         <v>4.5</v>
       </c>
       <c r="G7">
-        <f t="shared" ref="G6:G10" si="2">$J$5*F7</f>
+        <f t="shared" ref="G7:G10" si="2">$J$5*F7</f>
         <v>17.319949021896008</v>
       </c>
       <c r="H7">

--- a/analysis/analysis.xlsx
+++ b/analysis/analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasaray/Desktop/TeX/Physics_Laboratory/douji_sokutei/analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasaray/Desktop/TeX/Physics_Laboratory/douji_keisoku/analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97511708-4ABD-9947-AB0F-D84F586F3845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17CC49D-9B2A-BD41-8072-6E0FCDD2114F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="800" yWindow="680" windowWidth="28600" windowHeight="18440" activeTab="4" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
+    <workbookView xWindow="820" yWindow="700" windowWidth="28580" windowHeight="18420" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/analysis/analysis.xlsx
+++ b/analysis/analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasaray/Desktop/TeX/Physics_Laboratory/douji_keisoku/analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17CC49D-9B2A-BD41-8072-6E0FCDD2114F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6E7C44-F949-FC47-B1AD-AD12248A1F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="820" yWindow="700" windowWidth="28580" windowHeight="18420" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
+    <workbookView xWindow="900" yWindow="2860" windowWidth="28580" windowHeight="18420" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4682,6 +4682,12 @@
         <v>4.5642541425258649</v>
       </c>
     </row>
+    <row r="15" spans="1:8">
+      <c r="H15">
+        <f>(G21-F4)/E4</f>
+        <v>48.289755394382283</v>
+      </c>
+    </row>
     <row r="16" spans="1:8">
       <c r="H16">
         <f>(G22-F4)/E4</f>

--- a/analysis/analysis.xlsx
+++ b/analysis/analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasaray/Desktop/TeX/Physics_Laboratory/douji_keisoku/analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6E7C44-F949-FC47-B1AD-AD12248A1F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBE2218-DC55-464F-8150-3A46B06D14C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="2860" windowWidth="28580" windowHeight="18420" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
+    <workbookView xWindow="800" yWindow="700" windowWidth="28580" windowHeight="18420" activeTab="2" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/analysis/analysis.xlsx
+++ b/analysis/analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasaray/Desktop/TeX/Physics_Laboratory/douji_keisoku/analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBE2218-DC55-464F-8150-3A46B06D14C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F289FFB-1ECF-BA44-AF2F-7F78A2C39835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="800" yWindow="700" windowWidth="28580" windowHeight="18420" activeTab="2" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
+    <workbookView xWindow="820" yWindow="700" windowWidth="28580" windowHeight="18420" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4862,7 +4862,7 @@
         <v>257</v>
       </c>
       <c r="E24">
-        <f t="shared" ref="E24:E26" si="4">D24*$E$4+$F$4</f>
+        <f>D24*$E$4+$F$4</f>
         <v>973.63351042594343</v>
       </c>
       <c r="F24">
@@ -4877,7 +4877,7 @@
         <v>62</v>
       </c>
       <c r="I24">
-        <f t="shared" ref="I24:I26" si="5">H24*$E$4+$F$4</f>
+        <f t="shared" ref="I24:I26" si="4">H24*$E$4+$F$4</f>
         <v>223.10238614378304</v>
       </c>
       <c r="J24">
@@ -4921,7 +4921,7 @@
         <v>125</v>
       </c>
       <c r="E26">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="E24:E26" si="5">D26*$E$4+$F$4</f>
         <v>465.58167245032718</v>
       </c>
       <c r="F26">
@@ -4936,7 +4936,7 @@
         <v>56</v>
       </c>
       <c r="I26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>200.00912078125501</v>
       </c>
       <c r="J26">

--- a/analysis/analysis.xlsx
+++ b/analysis/analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasaray/Desktop/TeX/Physics_Laboratory/douji_keisoku/analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F289FFB-1ECF-BA44-AF2F-7F78A2C39835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C782F30-BBED-EC4A-8B36-26DECBE4190A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="820" yWindow="700" windowWidth="28580" windowHeight="18420" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4818,9 +4818,13 @@
         <f>B22/(1+(2*B22)/$F$10)</f>
         <v>212.84710878797779</v>
       </c>
+      <c r="H22">
+        <f>(G22-$F$4)/$E$4</f>
+        <v>59.335514784553816</v>
+      </c>
       <c r="J22">
         <f t="shared" ref="J22:J26" si="1">SQRT((H22*$E$5)^2+$F$5^2)</f>
-        <v>3.7878664857879132</v>
+        <v>3.8818144786085571</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4834,17 +4838,25 @@
         <f t="shared" ref="C23:C26" si="2">B23/(1+$F$10/(2*B23))</f>
         <v>39.427814569536423</v>
       </c>
+      <c r="D23">
+        <f>(C23-F4)/E4</f>
+        <v>14.278406187039163</v>
+      </c>
       <c r="F23">
         <f t="shared" si="0"/>
-        <v>3.7878664857879132</v>
+        <v>3.7933701862053026</v>
       </c>
       <c r="G23">
         <f t="shared" ref="G23:G26" si="3">B23/(1+(2*B23)/$F$10)</f>
         <v>82.572185430463577</v>
       </c>
+      <c r="H23">
+        <f>(G23-$F$4)/$E$4</f>
+        <v>25.488004357837859</v>
+      </c>
       <c r="J23">
         <f t="shared" si="1"/>
-        <v>3.7878664857879132</v>
+        <v>3.8053762282765642</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4893,17 +4905,25 @@
         <f t="shared" si="2"/>
         <v>1118.5955303745673</v>
       </c>
+      <c r="D25">
+        <f>(C25-F4)/E4</f>
+        <v>294.66345322056821</v>
+      </c>
       <c r="F25">
         <f t="shared" si="0"/>
-        <v>3.7878664857879132</v>
+        <v>5.667270314464699</v>
       </c>
       <c r="G25">
         <f t="shared" si="3"/>
         <v>214.4044696254328</v>
       </c>
+      <c r="H25">
+        <f>(G25-$F$4)/$E$4</f>
+        <v>59.740142059131109</v>
+      </c>
       <c r="J25">
         <f t="shared" si="1"/>
-        <v>3.7878664857879132</v>
+        <v>3.8830844025500015</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4921,7 +4941,7 @@
         <v>125</v>
       </c>
       <c r="E26">
-        <f t="shared" ref="E24:E26" si="5">D26*$E$4+$F$4</f>
+        <f t="shared" ref="E26" si="5">D26*$E$4+$F$4</f>
         <v>465.58167245032718</v>
       </c>
       <c r="F26">
